--- a/app/src/main/assets/methodmesh/odk_templates/signals/example_odk_showcase_signal_morse_transmit.xlsx
+++ b/app/src/main/assets/methodmesh/odk_templates/signals/example_odk_showcase_signal_morse_transmit.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R36da9906c0904e45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R30b5c28875314146"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R9ab116a2f81141e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R6c2ac8ad8bd54220"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rbf3fe9e283e04095"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Raccc200de8514682"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -358,7 +358,7 @@
         <x:v>field-list</x:v>
       </x:c>
       <x:c r="J3" s="8" t="str">
-        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='signal.morse.transmit',input_payload=${morse_tx_payload},input_route=${morse_tx_route},input_wpm=${morse_tx_wpm},input_tone_frequency_hz=${morse_tx_tone_hz},input_element_gap_units=${morse_tx_element_gap},input_letter_gap_units=${morse_tx_letter_gap},input_word_gap_units=${morse_tx_word_gap},input_loop_mode=${morse_tx_loop_mode},input_repeat_count=${morse_tx_repeat_count},input_loop_gap_units=${morse_tx_loop_gap},input_payload_mode='FULL',return_mode='flat')</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='signal.morse.transmit',input_payload=${morse_tx_payload},input_route=${morse_tx_route},input_wpm=${morse_tx_wpm},input_tone_frequency_hz=${morse_tx_tone_hz},input_colour_assist=${morse_tx_colour_assist},input_element_gap_units=${morse_tx_element_gap},input_letter_gap_units=${morse_tx_letter_gap},input_word_gap_units=${morse_tx_word_gap},input_loop_mode=${morse_tx_loop_mode},input_repeat_count=${morse_tx_repeat_count},input_loop_gap_units=${morse_tx_loop_gap},input_payload_mode='FULL',return_mode='flat')</x:v>
       </x:c>
       <x:c r="K3" s="8"/>
     </x:row>
@@ -372,7 +372,9 @@
       <x:c r="C4" s="8" t="str">
         <x:v>Message</x:v>
       </x:c>
-      <x:c r="D4" s="8"/>
+      <x:c r="D4" s="8" t="str">
+        <x:v>Example: hello, world</x:v>
+      </x:c>
       <x:c r="E4" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
@@ -454,21 +456,23 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="8" t="str">
-        <x:v>select_one element_gap</x:v>
+        <x:v>select_one yes_no</x:v>
       </x:c>
       <x:c r="B8" s="8" t="str">
-        <x:v>morse_tx_element_gap</x:v>
+        <x:v>morse_tx_colour_assist</x:v>
       </x:c>
       <x:c r="C8" s="8" t="str">
-        <x:v>Element gap</x:v>
+        <x:v>Screen colour assist</x:v>
       </x:c>
       <x:c r="D8" s="8" t="str">
-        <x:v>Independent quiet gap between dot/dash elements.</x:v>
+        <x:v>White dots/acquisition; red dashes/START/END. Morse timing remains canonical.</x:v>
       </x:c>
       <x:c r="E8" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="F8" s="8"/>
+      <x:c r="F8" s="8" t="str">
+        <x:v>${morse_tx_route}='screen' or ${morse_tx_route}='screen_sound' or ${morse_tx_route}='all'</x:v>
+      </x:c>
       <x:c r="G8" s="8"/>
       <x:c r="H8" s="8"/>
       <x:c r="I8" s="8"/>
@@ -477,16 +481,16 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="8" t="str">
-        <x:v>select_one letter_gap</x:v>
+        <x:v>select_one element_gap</x:v>
       </x:c>
       <x:c r="B9" s="8" t="str">
-        <x:v>morse_tx_letter_gap</x:v>
+        <x:v>morse_tx_element_gap</x:v>
       </x:c>
       <x:c r="C9" s="8" t="str">
-        <x:v>Letter gap</x:v>
+        <x:v>Element gap</x:v>
       </x:c>
       <x:c r="D9" s="8" t="str">
-        <x:v>Independent quiet gap between letters.</x:v>
+        <x:v>Independent quiet gap between dot/dash elements.</x:v>
       </x:c>
       <x:c r="E9" s="8" t="str">
         <x:v>yes</x:v>
@@ -500,16 +504,16 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="8" t="str">
-        <x:v>select_one word_gap</x:v>
+        <x:v>select_one letter_gap</x:v>
       </x:c>
       <x:c r="B10" s="8" t="str">
-        <x:v>morse_tx_word_gap</x:v>
+        <x:v>morse_tx_letter_gap</x:v>
       </x:c>
       <x:c r="C10" s="8" t="str">
-        <x:v>Word gap</x:v>
+        <x:v>Letter gap</x:v>
       </x:c>
       <x:c r="D10" s="8" t="str">
-        <x:v>Independent quiet gap between words.</x:v>
+        <x:v>Independent quiet gap between letters.</x:v>
       </x:c>
       <x:c r="E10" s="8" t="str">
         <x:v>yes</x:v>
@@ -523,15 +527,17 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="8" t="str">
-        <x:v>select_one loop_mode</x:v>
+        <x:v>select_one word_gap</x:v>
       </x:c>
       <x:c r="B11" s="8" t="str">
-        <x:v>morse_tx_loop_mode</x:v>
+        <x:v>morse_tx_word_gap</x:v>
       </x:c>
       <x:c r="C11" s="8" t="str">
-        <x:v>Loop mode</x:v>
-      </x:c>
-      <x:c r="D11" s="8"/>
+        <x:v>Word gap</x:v>
+      </x:c>
+      <x:c r="D11" s="8" t="str">
+        <x:v>Independent quiet gap between words.</x:v>
+      </x:c>
       <x:c r="E11" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
@@ -544,21 +550,19 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="8" t="str">
-        <x:v>select_one repeat_morse</x:v>
+        <x:v>select_one loop_mode</x:v>
       </x:c>
       <x:c r="B12" s="8" t="str">
-        <x:v>morse_tx_repeat_count</x:v>
+        <x:v>morse_tx_loop_mode</x:v>
       </x:c>
       <x:c r="C12" s="8" t="str">
-        <x:v>Repeat count</x:v>
+        <x:v>Loop mode</x:v>
       </x:c>
       <x:c r="D12" s="8"/>
       <x:c r="E12" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="F12" s="8" t="str">
-        <x:v>${morse_tx_loop_mode}='count'</x:v>
-      </x:c>
+      <x:c r="F12" s="8"/>
       <x:c r="G12" s="8"/>
       <x:c r="H12" s="8"/>
       <x:c r="I12" s="8"/>
@@ -567,21 +571,21 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="8" t="str">
-        <x:v>select_one cycle_gap</x:v>
+        <x:v>select_one repeat_morse</x:v>
       </x:c>
       <x:c r="B13" s="8" t="str">
-        <x:v>morse_tx_loop_gap</x:v>
+        <x:v>morse_tx_repeat_count</x:v>
       </x:c>
       <x:c r="C13" s="8" t="str">
-        <x:v>Cycle gap</x:v>
-      </x:c>
-      <x:c r="D13" s="8" t="str">
-        <x:v>Quiet units between complete START→END cycles.</x:v>
-      </x:c>
+        <x:v>Repeat count</x:v>
+      </x:c>
+      <x:c r="D13" s="8"/>
       <x:c r="E13" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="F13" s="8"/>
+      <x:c r="F13" s="8" t="str">
+        <x:v>${morse_tx_loop_mode}='count'</x:v>
+      </x:c>
       <x:c r="G13" s="8"/>
       <x:c r="H13" s="8"/>
       <x:c r="I13" s="8"/>
@@ -590,38 +594,36 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>select_one cycle_gap</x:v>
       </x:c>
       <x:c r="B14" s="8" t="str">
-        <x:v>methodmesh_status</x:v>
+        <x:v>morse_tx_loop_gap</x:v>
       </x:c>
       <x:c r="C14" s="8" t="str">
-        <x:v>MethodMesh status</x:v>
+        <x:v>Cycle gap</x:v>
       </x:c>
       <x:c r="D14" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
-      </x:c>
-      <x:c r="E14" s="8"/>
+        <x:v>Quiet units between complete START→END cycles.</x:v>
+      </x:c>
+      <x:c r="E14" s="8" t="str">
+        <x:v>yes</x:v>
+      </x:c>
       <x:c r="F14" s="8"/>
       <x:c r="G14" s="8"/>
       <x:c r="H14" s="8"/>
-      <x:c r="I14" s="8" t="str">
-        <x:v>hidden-answer</x:v>
-      </x:c>
+      <x:c r="I14" s="8"/>
       <x:c r="J14" s="8"/>
-      <x:c r="K14" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
+      <x:c r="K14" s="8"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B15" s="8" t="str">
-        <x:v>signal_morse_result</x:v>
+        <x:v>methodmesh_status</x:v>
       </x:c>
       <x:c r="C15" s="8" t="str">
-        <x:v>signal_morse_result</x:v>
+        <x:v>MethodMesh status</x:v>
       </x:c>
       <x:c r="D15" s="8" t="str">
         <x:v>Returned by MethodMesh.</x:v>
@@ -643,10 +645,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B16" s="8" t="str">
-        <x:v>signal_morse_payload</x:v>
+        <x:v>signal_morse_result</x:v>
       </x:c>
       <x:c r="C16" s="8" t="str">
-        <x:v>signal_morse_payload</x:v>
+        <x:v>signal_morse_result</x:v>
       </x:c>
       <x:c r="D16" s="8" t="str">
         <x:v>Returned by MethodMesh.</x:v>
@@ -668,10 +670,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B17" s="8" t="str">
-        <x:v>signal_morse_notation</x:v>
+        <x:v>signal_morse_payload</x:v>
       </x:c>
       <x:c r="C17" s="8" t="str">
-        <x:v>signal_morse_notation</x:v>
+        <x:v>signal_morse_payload</x:v>
       </x:c>
       <x:c r="D17" s="8" t="str">
         <x:v>Returned by MethodMesh.</x:v>
@@ -693,10 +695,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B18" s="8" t="str">
-        <x:v>signal_morse_route</x:v>
+        <x:v>signal_morse_notation</x:v>
       </x:c>
       <x:c r="C18" s="8" t="str">
-        <x:v>signal_morse_route</x:v>
+        <x:v>signal_morse_notation</x:v>
       </x:c>
       <x:c r="D18" s="8" t="str">
         <x:v>Returned by MethodMesh.</x:v>
@@ -715,13 +717,13 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="8" t="str">
-        <x:v>integer</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="B19" s="8" t="str">
-        <x:v>signal_morse_wpm</x:v>
+        <x:v>signal_morse_route</x:v>
       </x:c>
       <x:c r="C19" s="8" t="str">
-        <x:v>signal_morse_wpm</x:v>
+        <x:v>signal_morse_route</x:v>
       </x:c>
       <x:c r="D19" s="8" t="str">
         <x:v>Returned by MethodMesh.</x:v>
@@ -743,10 +745,10 @@
         <x:v>integer</x:v>
       </x:c>
       <x:c r="B20" s="8" t="str">
-        <x:v>signal_morse_repetitions</x:v>
+        <x:v>signal_morse_wpm</x:v>
       </x:c>
       <x:c r="C20" s="8" t="str">
-        <x:v>signal_morse_repetitions</x:v>
+        <x:v>signal_morse_wpm</x:v>
       </x:c>
       <x:c r="D20" s="8" t="str">
         <x:v>Returned by MethodMesh.</x:v>
@@ -765,13 +767,13 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>integer</x:v>
       </x:c>
       <x:c r="B21" s="8" t="str">
-        <x:v>signal_morse_status</x:v>
+        <x:v>signal_morse_repetitions</x:v>
       </x:c>
       <x:c r="C21" s="8" t="str">
-        <x:v>signal_morse_status</x:v>
+        <x:v>signal_morse_repetitions</x:v>
       </x:c>
       <x:c r="D21" s="8" t="str">
         <x:v>Returned by MethodMesh.</x:v>
@@ -793,10 +795,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B22" s="8" t="str">
-        <x:v>signal_morse_error</x:v>
+        <x:v>signal_morse_status</x:v>
       </x:c>
       <x:c r="C22" s="8" t="str">
-        <x:v>signal_morse_error</x:v>
+        <x:v>signal_morse_status</x:v>
       </x:c>
       <x:c r="D22" s="8" t="str">
         <x:v>Returned by MethodMesh.</x:v>
@@ -818,13 +820,13 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B23" t="str">
-        <x:v>methodmesh_full_json</x:v>
+        <x:v>signal_morse_error</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>Full MethodMesh JSON</x:v>
+        <x:v>signal_morse_error</x:v>
       </x:c>
       <x:c r="D23" t="str">
-        <x:v>Complete execution result with provenance.</x:v>
+        <x:v>Returned by MethodMesh.</x:v>
       </x:c>
       <x:c r="E23"/>
       <x:c r="F23"/>
@@ -840,34 +842,38 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
-        <x:v>end group</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="B24" t="str">
-        <x:v>run_signal_end</x:v>
-      </x:c>
-      <x:c r="C24"/>
-      <x:c r="D24"/>
+        <x:v>methodmesh_full_json</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>Full MethodMesh JSON</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>Complete execution result with provenance.</x:v>
+      </x:c>
       <x:c r="E24"/>
       <x:c r="F24"/>
       <x:c r="G24"/>
       <x:c r="H24"/>
-      <x:c r="I24"/>
+      <x:c r="I24" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
       <x:c r="J24"/>
-      <x:c r="K24"/>
+      <x:c r="K24" t="str">
+        <x:v>yes</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
-        <x:v>note</x:v>
+        <x:v>end group</x:v>
       </x:c>
       <x:c r="B25" t="str">
-        <x:v>return_summary</x:v>
-      </x:c>
-      <x:c r="C25" t="str">
-        <x:v>MethodMesh result captured.</x:v>
-      </x:c>
-      <x:c r="D25" t="str">
-        <x:v>Use methodmesh_full_json for the complete provenance record.</x:v>
-      </x:c>
+        <x:v>run_signal_end</x:v>
+      </x:c>
+      <x:c r="C25"/>
+      <x:c r="D25"/>
       <x:c r="E25"/>
       <x:c r="F25"/>
       <x:c r="G25"/>
@@ -875,6 +881,27 @@
       <x:c r="I25"/>
       <x:c r="J25"/>
       <x:c r="K25"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>note</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>return_summary</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>MethodMesh result captured.</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>Use methodmesh_full_json for the complete provenance record.</x:v>
+      </x:c>
+      <x:c r="E26"/>
+      <x:c r="F26"/>
+      <x:c r="G26"/>
+      <x:c r="H26"/>
+      <x:c r="I26"/>
+      <x:c r="J26"/>
+      <x:c r="K26"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1264,6 +1291,28 @@
         <x:v>24 units</x:v>
       </x:c>
     </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>yes_no</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>On</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>yes_no</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1297,7 +1346,7 @@
         <x:v>signals_signal_morse_transmit</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>2026090906</x:v>
+        <x:v>2026091101</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
